--- a/artfynd/A 29119-2025 artfynd.xlsx
+++ b/artfynd/A 29119-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1981271</v>
+        <v>1321557</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514242.811294396</v>
+        <v>514334</v>
       </c>
       <c r="R2" t="n">
-        <v>6992786.044070287</v>
+        <v>6992778</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2011-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,16 +784,11 @@
         <v>1856295</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514307.8193323846</v>
+        <v>514308</v>
       </c>
       <c r="R3" t="n">
-        <v>6992767.287052128</v>
+        <v>6992767</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,19 +858,9 @@
           <t>2011-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,42 +887,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1981272</v>
+        <v>1856296</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514180.9610376132</v>
+        <v>514181</v>
       </c>
       <c r="R4" t="n">
-        <v>6992913.628829149</v>
+        <v>6992914</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,19 +964,9 @@
           <t>2011-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1856296</v>
+        <v>1981271</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,26 +1004,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514180.9610376132</v>
+        <v>514243</v>
       </c>
       <c r="R5" t="n">
-        <v>6992913.628829149</v>
+        <v>6992786</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,19 +1070,9 @@
           <t>2011-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,6 +1096,112 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1981272</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ismundsundet, Söder om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>514181</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6992914</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-09-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-09-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29119-2025 artfynd.xlsx
+++ b/artfynd/A 29119-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1321557</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1856295</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1856296</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1981271</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1981272</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>